--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -20965,16 +20965,16 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O117" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0.06953107914299034</v>
+        <v>0.08256815648230102</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -22606,12 +22606,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22645,16 +22645,16 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O127" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>0.003438045759323263</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -22687,40 +22687,188 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>12</v>
+      </c>
+      <c r="O128" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.003438045759323263</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
+      <c r="AT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW127" t="inlineStr">
+      <c r="AW128" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
+      <c r="AX128" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY127" t="inlineStr">
+      <c r="AY128" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
+      <c r="AZ128" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA127" t="inlineStr">
+      <c r="BA128" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB127" t="inlineStr">
+      <c r="BB128" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC127" t="inlineStr">
+      <c r="BC128" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -22842,7 +22990,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -22852,7 +23000,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
@@ -22904,7 +23052,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>6</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>5</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.05550746142397953</v>
       </c>
@@ -1454,9 +1448,6 @@
       <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.08894045854320688</v>
       </c>
@@ -1850,9 +1841,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1998,9 +1986,6 @@
       <c r="O9" t="n">
         <v>6</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.1061385495477304</v>
       </c>
@@ -2643,7 +2628,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -2790,9 +2775,6 @@
       <c r="O13" t="n">
         <v>15</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.1401732064242502</v>
       </c>
@@ -4222,9 +4204,6 @@
       <c r="O22" t="n">
         <v>4</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4615,9 +4594,6 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.01110149228479591</v>
       </c>
@@ -4763,9 +4739,6 @@
       <c r="O25" t="n">
         <v>2</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -5159,9 +5132,6 @@
       <c r="O27" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -5307,9 +5277,6 @@
       <c r="O28" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.03537951651591013</v>
       </c>
@@ -5952,7 +5919,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6099,9 +6066,6 @@
       <c r="O32" t="n">
         <v>6</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.05606928256970008</v>
       </c>
@@ -7383,9 +7347,6 @@
       <c r="O40" t="n">
         <v>2</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7776,9 +7737,6 @@
       <c r="O42" t="n">
         <v>4</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.04440596913918363</v>
       </c>
@@ -7924,9 +7882,6 @@
       <c r="O43" t="n">
         <v>6</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.1067285502518482</v>
       </c>
@@ -8320,9 +8275,6 @@
       <c r="O45" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -8468,9 +8420,6 @@
       <c r="O46" t="n">
         <v>3</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.05306927477386519</v>
       </c>
@@ -9113,7 +9062,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -9260,9 +9209,6 @@
       <c r="O50" t="n">
         <v>2</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -10396,9 +10342,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -10544,9 +10487,6 @@
       <c r="O58" t="n">
         <v>4</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10937,9 +10877,6 @@
       <c r="O60" t="n">
         <v>3</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.03330447685438772</v>
       </c>
@@ -11085,9 +11022,6 @@
       <c r="O61" t="n">
         <v>2</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -11481,9 +11415,6 @@
       <c r="O63" t="n">
         <v>1</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -11629,9 +11560,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12025,9 +11953,6 @@
       <c r="O66" t="n">
         <v>2</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.03782520932943658</v>
       </c>
@@ -12274,7 +12199,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -12421,9 +12346,6 @@
       <c r="O68" t="n">
         <v>6</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.05606928256970008</v>
       </c>
@@ -12817,9 +12739,6 @@
       <c r="O70" t="n">
         <v>16</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.06953107914299034</v>
       </c>
@@ -13557,9 +13476,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -13705,9 +13621,6 @@
       <c r="O76" t="n">
         <v>5</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14098,9 +14011,6 @@
       <c r="O78" t="n">
         <v>2</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.02220298456959181</v>
       </c>
@@ -14246,9 +14156,6 @@
       <c r="O79" t="n">
         <v>5</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.08894045854320688</v>
       </c>
@@ -14642,9 +14549,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -14790,9 +14694,6 @@
       <c r="O82" t="n">
         <v>5</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.08844879128977531</v>
       </c>
@@ -15186,9 +15087,6 @@
       <c r="O84" t="n">
         <v>2</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.03782520932943658</v>
       </c>
@@ -15435,7 +15333,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -15582,9 +15480,6 @@
       <c r="O86" t="n">
         <v>7</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.06541416299798342</v>
       </c>
@@ -15978,9 +15873,6 @@
       <c r="O88" t="n">
         <v>20</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.08691384892873792</v>
       </c>
@@ -16718,9 +16610,6 @@
       <c r="O93" t="n">
         <v>3</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -16866,9 +16755,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -17014,9 +16900,6 @@
       <c r="O95" t="n">
         <v>4</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.04440596913918363</v>
       </c>
@@ -17162,9 +17045,6 @@
       <c r="O96" t="n">
         <v>7</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.1245166419604896</v>
       </c>
@@ -17558,9 +17438,6 @@
       <c r="O98" t="n">
         <v>3</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -17706,9 +17583,6 @@
       <c r="O99" t="n">
         <v>3</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.05306927477386519</v>
       </c>
@@ -18102,9 +17976,6 @@
       <c r="O101" t="n">
         <v>5</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.09456302332359146</v>
       </c>
@@ -18351,7 +18222,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -18498,9 +18369,6 @@
       <c r="O103" t="n">
         <v>8</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.07475904342626677</v>
       </c>
@@ -18894,9 +18762,6 @@
       <c r="O105" t="n">
         <v>13</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.05649400180367965</v>
       </c>
@@ -19042,9 +18907,6 @@
       <c r="O106" t="n">
         <v>4</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -19190,9 +19052,6 @@
       <c r="O107" t="n">
         <v>10</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.002865038132769385</v>
       </c>
@@ -19338,9 +19197,6 @@
       <c r="O108" t="n">
         <v>13</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.003724549572600201</v>
       </c>
@@ -19486,9 +19342,6 @@
       <c r="O109" t="n">
         <v>12</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.003438045759323263</v>
       </c>
@@ -19634,9 +19487,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -19782,9 +19632,6 @@
       <c r="O111" t="n">
         <v>5</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.08894045854320688</v>
       </c>
@@ -20178,9 +20025,6 @@
       <c r="O113" t="n">
         <v>8</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.1415180660636405</v>
       </c>
@@ -20574,9 +20418,6 @@
       <c r="O115" t="n">
         <v>15</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.1401732064242502</v>
       </c>
@@ -20970,9 +20811,6 @@
       <c r="O117" t="n">
         <v>19</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.08256815648230102</v>
       </c>
@@ -21118,9 +20956,6 @@
       <c r="O118" t="n">
         <v>6</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -21266,9 +21101,6 @@
       <c r="O119" t="n">
         <v>14</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.00401105338587714</v>
       </c>
@@ -21414,9 +21246,6 @@
       <c r="O120" t="n">
         <v>8</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.002292030506215508</v>
       </c>
@@ -21562,9 +21391,6 @@
       <c r="O121" t="n">
         <v>14</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.00401105338587714</v>
       </c>
@@ -21710,9 +21536,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -21858,9 +21681,6 @@
       <c r="O123" t="n">
         <v>1</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -22249,16 +22069,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O125" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R125" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -22411,10 +22228,10 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -22650,9 +22467,6 @@
       <c r="O127" t="n">
         <v>1</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -22798,9 +22612,6 @@
       <c r="O128" t="n">
         <v>12</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.003438045759323263</v>
       </c>
@@ -22869,6 +22680,151 @@
         </is>
       </c>
       <c r="BC128" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>3</v>
+      </c>
+      <c r="O129" t="n">
+        <v>3</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.0008595114398308156</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr"/>
+      <c r="AT129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -22907,7 +22863,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -22990,7 +22946,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -23000,7 +22956,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -23052,7 +23008,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -16856,12 +16856,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -16895,81 +16895,92 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O95" t="n">
-        <v>4</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0.04440596913918363</v>
+        <v>3</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16996,17 +17007,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -17040,22 +17051,39 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O96" t="n">
-        <v>7</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0.1245166419604896</v>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_210</t>
+          <t>SER_CA_ON_PHO_IDTO_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -17063,6 +17091,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary listeriosis notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN96" t="b">
+        <v>1</v>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -17075,12 +17161,12 @@
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_210</t>
+          <t>SER_CA_ON_PHO_IDTO_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT96" t="n">
@@ -17088,47 +17174,47 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17155,17 +17241,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -17199,170 +17285,81 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O97" t="n">
-        <v>7</v>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>Listeria</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD97" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE97" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF97" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG97" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN97" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0.04440596913918363</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -17394,12 +17391,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -17433,81 +17430,95 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O98" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R98" t="n">
-        <v>0.04065810840590128</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17534,17 +17545,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -17578,22 +17589,39 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O99" t="n">
-        <v>3</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0.05306927477386519</v>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Listeria</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -17601,6 +17629,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN99" t="b">
+        <v>1</v>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -17613,12 +17699,12 @@
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT99" t="n">
@@ -17626,47 +17712,47 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17693,17 +17779,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -17742,165 +17828,76 @@
       <c r="O100" t="n">
         <v>3</v>
       </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>Listeriose</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD100" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF100" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG100" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN100" t="b">
-        <v>1</v>
+      <c r="R100" t="n">
+        <v>0.04065810840590128</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17932,12 +17929,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -17971,13 +17968,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O101" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R101" t="n">
-        <v>0.09456302332359146</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -17986,7 +17983,7 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -18011,7 +18008,7 @@
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -18024,42 +18021,42 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18091,12 +18088,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -18130,29 +18127,29 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O102" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Listeriose</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
@@ -18162,7 +18159,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -18177,7 +18174,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
@@ -18212,17 +18209,17 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly listeriosis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -18245,7 +18242,7 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT102" t="n">
@@ -18258,42 +18255,42 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18325,12 +18322,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -18364,13 +18361,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O103" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R103" t="n">
-        <v>0.07475904342626677</v>
+        <v>0.09456302332359146</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -18379,7 +18376,7 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -18404,7 +18401,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT103" t="n">
@@ -18417,42 +18414,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18484,12 +18481,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -18523,29 +18520,29 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O104" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>Listeriainfektion</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -18555,7 +18552,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -18570,7 +18567,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr">
@@ -18605,17 +18602,17 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly listeriosis notifications.</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -18638,7 +18635,7 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT104" t="n">
@@ -18651,42 +18648,42 @@
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18718,12 +18715,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -18757,81 +18754,95 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O105" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R105" t="n">
-        <v>0.05649400180367965</v>
+        <v>0.07475904342626677</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18858,17 +18869,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -18893,7 +18904,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -18902,81 +18913,170 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O106" t="n">
-        <v>4</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0.001146015253107754</v>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>Listeriainfektion</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN106" t="b">
+        <v>1</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19008,12 +19108,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -19038,7 +19138,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -19047,13 +19147,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O107" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R107" t="n">
-        <v>0.002865038132769385</v>
+        <v>0.05649400180367965</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -19086,42 +19186,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -19183,7 +19283,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -19192,13 +19292,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O108" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="R108" t="n">
-        <v>0.003724549572600201</v>
+        <v>0.001146015253107754</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -19328,7 +19428,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -19337,13 +19437,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O109" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R109" t="n">
-        <v>0.003438045759323263</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -19443,12 +19543,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -19473,22 +19573,22 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -19521,42 +19621,42 @@
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19588,12 +19688,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -19618,104 +19718,90 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O111" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R111" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.003438045759323263</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19742,17 +19828,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -19786,170 +19872,81 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>5</v>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Listeria</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP112" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AT112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV112" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19981,12 +19978,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20020,13 +20017,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O113" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R113" t="n">
-        <v>0.1415180660636405</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -20035,7 +20032,7 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -20055,12 +20052,12 @@
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT113" t="n">
@@ -20068,47 +20065,47 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20140,12 +20137,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20179,29 +20176,29 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O114" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>Listeriose</t>
+          <t>Listeria</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -20226,7 +20223,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr">
@@ -20261,17 +20258,17 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -20289,12 +20286,12 @@
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT114" t="n">
@@ -20302,47 +20299,47 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20374,12 +20371,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20413,13 +20410,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O115" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="R115" t="n">
-        <v>0.1401732064242502</v>
+        <v>0.1415180660636405</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -20428,7 +20425,7 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -20453,7 +20450,7 @@
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT115" t="n">
@@ -20466,42 +20463,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20533,12 +20530,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20572,29 +20569,29 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O116" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>Listeriainfektion</t>
+          <t>Listeriose</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -20619,7 +20616,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
@@ -20654,17 +20651,17 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -20687,7 +20684,7 @@
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT116" t="n">
@@ -20700,42 +20697,42 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20767,12 +20764,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20806,81 +20803,95 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="O117" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="R117" t="n">
-        <v>0.08256815648230102</v>
+        <v>0.1401732064242502</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -20907,17 +20918,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20942,7 +20953,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -20951,81 +20962,170 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O118" t="n">
-        <v>6</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0.001719022879661631</v>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Listeriainfektion</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21057,12 +21157,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21087,7 +21187,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -21096,13 +21196,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O119" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="R119" t="n">
-        <v>0.00401105338587714</v>
+        <v>0.08256815648230102</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -21135,42 +21235,42 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21232,7 +21332,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -21241,13 +21341,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O120" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R120" t="n">
-        <v>0.002292030506215508</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -21377,7 +21477,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -21492,12 +21592,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21522,22 +21622,22 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>0.002292030506215508</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21570,42 +21670,42 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21637,12 +21737,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21667,104 +21767,90 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O123" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R123" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.00401105338587714</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21791,17 +21877,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21835,170 +21921,81 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>1</v>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>Listeria</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD124" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG124" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN124" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP124" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AT124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV124" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22030,12 +22027,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -22069,13 +22066,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R125" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -22084,7 +22081,7 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -22104,12 +22101,12 @@
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT125" t="n">
@@ -22117,47 +22114,47 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22189,12 +22186,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -22228,29 +22225,29 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>Listeriose</t>
+          <t>Listeria</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
@@ -22275,7 +22272,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
@@ -22310,17 +22307,17 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -22338,12 +22335,12 @@
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT126" t="n">
@@ -22351,47 +22348,47 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22423,12 +22420,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22462,81 +22459,95 @@
         </is>
       </c>
       <c r="N127" t="n">
+        <v>2</v>
+      </c>
+      <c r="O127" t="n">
+        <v>2</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
         <v>1</v>
       </c>
-      <c r="O127" t="n">
-        <v>1</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP127" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
-      <c r="AT127" t="n">
-        <v>0</v>
-      </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22563,17 +22574,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22607,81 +22618,170 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O128" t="n">
-        <v>12</v>
-      </c>
-      <c r="R128" t="n">
-        <v>0.003438045759323263</v>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>Listeriose</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN128" t="b">
+        <v>1</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22713,12 +22813,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22743,7 +22843,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22752,13 +22852,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R129" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22791,40 +22891,330 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>12</v>
+      </c>
+      <c r="O130" t="n">
+        <v>12</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.003438045759323263</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr"/>
+      <c r="AT130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW129" t="inlineStr">
+      <c r="AW130" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
+      <c r="AX130" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY129" t="inlineStr">
+      <c r="AY130" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
+      <c r="AZ130" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA129" t="inlineStr">
+      <c r="BA130" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB129" t="inlineStr">
+      <c r="BB130" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC129" t="inlineStr">
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>3</v>
+      </c>
+      <c r="O131" t="n">
+        <v>3</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.0008595114398308156</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
+      <c r="AT131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -22946,7 +23336,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -22956,7 +23346,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -22976,7 +23366,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -23008,7 +23398,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -22852,13 +22852,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R129" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -23220,6 +23220,151 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>13</v>
+      </c>
+      <c r="O132" t="n">
+        <v>13</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.003724549572600201</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr"/>
+      <c r="AT132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23253,7 +23398,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -23336,7 +23481,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
@@ -23346,7 +23491,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
@@ -23398,7 +23543,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>494</v>
+        <v>507</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -20764,12 +20764,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20803,13 +20803,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O117" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="R117" t="n">
-        <v>0.1401732064242502</v>
+        <v>0.132388232653028</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -20843,7 +20843,7 @@
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT117" t="n">
@@ -20856,42 +20856,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20923,12 +20923,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20962,29 +20962,29 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O118" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>Listeriainfektion</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
@@ -20994,7 +20994,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -21009,7 +21009,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
@@ -21044,17 +21044,17 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly listeriosis notifications.</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -21077,7 +21077,7 @@
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT118" t="n">
@@ -21090,42 +21090,42 @@
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21157,12 +21157,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21196,81 +21196,95 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="O119" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="R119" t="n">
-        <v>0.08256815648230102</v>
+        <v>0.1401732064242502</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21297,17 +21311,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -21332,7 +21346,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -21341,81 +21355,170 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O120" t="n">
-        <v>6</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0.001719022879661631</v>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Listeriainfektion</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21447,12 +21550,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -21477,7 +21580,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -21486,13 +21589,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O121" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="R121" t="n">
-        <v>0.00401105338587714</v>
+        <v>0.08256815648230102</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -21525,42 +21628,42 @@
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21622,7 +21725,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -21631,13 +21734,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O122" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R122" t="n">
-        <v>0.002292030506215508</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21767,7 +21870,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -21882,12 +21985,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21912,22 +22015,22 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>0.002292030506215508</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -21960,42 +22063,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22027,12 +22130,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -22057,104 +22160,90 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N125" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O125" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R125" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.00401105338587714</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22181,17 +22270,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -22225,170 +22314,81 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>1</v>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>Listeria</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN126" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP126" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AT126" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV126" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22420,12 +22420,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22459,13 +22459,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R127" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -22494,12 +22494,12 @@
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT127" t="n">
@@ -22507,47 +22507,47 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22579,12 +22579,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22618,29 +22618,29 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>Listeriose</t>
+          <t>Listeria</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -22665,7 +22665,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
@@ -22700,17 +22700,17 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -22728,12 +22728,12 @@
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT128" t="n">
@@ -22741,47 +22741,47 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22813,12 +22813,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22852,81 +22852,95 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R129" t="n">
-        <v>0.008691384892873792</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22953,17 +22967,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22997,81 +23011,170 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O130" t="n">
-        <v>12</v>
-      </c>
-      <c r="R130" t="n">
-        <v>0.003438045759323263</v>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>Listeriose</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN130" t="b">
+        <v>1</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23103,12 +23206,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -23133,7 +23236,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -23142,13 +23245,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R131" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -23181,42 +23284,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23278,7 +23381,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -23287,13 +23390,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O132" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R132" t="n">
-        <v>0.003724549572600201</v>
+        <v>0.003438045759323263</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -23360,6 +23463,296 @@
         </is>
       </c>
       <c r="BC132" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>3</v>
+      </c>
+      <c r="O133" t="n">
+        <v>3</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.0008595114398308156</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr"/>
+      <c r="AT133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>13</v>
+      </c>
+      <c r="O134" t="n">
+        <v>13</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.003724549572600201</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
+      <c r="AT134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -23481,7 +23874,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
@@ -23491,7 +23884,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -23511,7 +23904,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -23543,7 +23936,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>507</v>
+        <v>516</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -23758,6 +23758,151 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>9</v>
+      </c>
+      <c r="O135" t="n">
+        <v>9</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.002578534319492447</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23791,7 +23936,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -23874,7 +24019,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
@@ -23884,7 +24029,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -23936,7 +24081,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>516</v>
+        <v>525</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -20371,12 +20371,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20410,95 +20410,81 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O115" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R115" t="n">
-        <v>0.1415180660636405</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20525,7 +20511,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -20574,98 +20560,23 @@
       <c r="O116" t="n">
         <v>8</v>
       </c>
+      <c r="R116" t="n">
+        <v>0.1415180660636405</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>Listeriose</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE116" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF116" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG116" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN116" t="b">
-        <v>1</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -20759,17 +20670,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20803,22 +20714,39 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O117" t="n">
-        <v>7</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0.132388232653028</v>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Listeriose</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -20826,6 +20754,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN117" t="b">
+        <v>1</v>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -20843,7 +20829,7 @@
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT117" t="n">
@@ -20856,42 +20842,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20918,7 +20904,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -20967,98 +20953,23 @@
       <c r="O118" t="n">
         <v>7</v>
       </c>
+      <c r="R118" t="n">
+        <v>0.132388232653028</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>Listeriosis</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly listeriosis notifications.</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN118" t="b">
-        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -21152,17 +21063,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21196,22 +21107,39 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O119" t="n">
-        <v>15</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0.1401732064242502</v>
-      </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -21219,6 +21147,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly listeriosis notifications.</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN119" t="b">
+        <v>1</v>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -21236,7 +21222,7 @@
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT119" t="n">
@@ -21249,42 +21235,42 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21311,7 +21297,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -21360,98 +21346,23 @@
       <c r="O120" t="n">
         <v>15</v>
       </c>
+      <c r="R120" t="n">
+        <v>0.1401732064242502</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>Listeriainfektion</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD120" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG120" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN120" t="b">
-        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -21545,17 +21456,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -21589,81 +21500,170 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="O121" t="n">
-        <v>19</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0.08256815648230102</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Listeriainfektion</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21695,12 +21695,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21725,7 +21725,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -21734,13 +21734,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="O122" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="R122" t="n">
-        <v>0.001719022879661631</v>
+        <v>0.08256815648230102</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21773,42 +21773,42 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21870,7 +21870,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -21879,13 +21879,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O123" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R123" t="n">
-        <v>0.00401105338587714</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -22024,13 +22024,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O124" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="R124" t="n">
-        <v>0.002292030506215508</v>
+        <v>0.00401105338587714</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -22169,13 +22169,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O125" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R125" t="n">
-        <v>0.00401105338587714</v>
+        <v>0.002292030506215508</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -22275,12 +22275,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -22305,22 +22305,22 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>0.00401105338587714</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -22353,42 +22353,42 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22420,12 +22420,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22459,95 +22459,81 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>0.01778809170864137</v>
+        <v>0</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22560,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -22623,98 +22609,23 @@
       <c r="O128" t="n">
         <v>1</v>
       </c>
+      <c r="R128" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U128" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>Listeria</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG128" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN128" t="b">
-        <v>1</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -22808,17 +22719,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22852,22 +22763,39 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O129" t="n">
-        <v>4</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0.07075903303182025</v>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Listeria</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -22875,6 +22803,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -22887,12 +22873,12 @@
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT129" t="n">
@@ -22900,47 +22886,47 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22967,7 +22953,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -23016,98 +23002,23 @@
       <c r="O130" t="n">
         <v>4</v>
       </c>
+      <c r="R130" t="n">
+        <v>0.07075903303182025</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>Listeriose</t>
-        </is>
-      </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD130" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE130" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF130" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG130" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN130" t="b">
-        <v>1</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -23201,17 +23112,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -23245,81 +23156,170 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O131" t="n">
-        <v>2</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0.008691384892873792</v>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Listeriose</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
+        <v>1</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23351,12 +23351,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -23390,13 +23390,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O132" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R132" t="n">
-        <v>0.003438045759323263</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -23429,42 +23429,42 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23526,7 +23526,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -23535,13 +23535,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O133" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R133" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.003438045759323263</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -23680,13 +23680,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O134" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="R134" t="n">
-        <v>0.003724549572600201</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -23825,13 +23825,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O135" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R135" t="n">
-        <v>0.002578534319492447</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23898,6 +23898,151 @@
         </is>
       </c>
       <c r="BC135" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>9</v>
+      </c>
+      <c r="O136" t="n">
+        <v>9</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.002578534319492447</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
+      <c r="AT136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -24019,7 +24164,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -24029,7 +24174,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -24081,7 +24226,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1481,17 +1481,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1707,7 +1712,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1715,17 +1720,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2011,7 +2021,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2019,17 +2029,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2245,7 +2260,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2253,17 +2268,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2800,7 +2820,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2808,17 +2828,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3034,7 +3059,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -3042,17 +3067,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -4764,7 +4794,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -4772,17 +4802,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -4998,7 +5033,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -5006,17 +5041,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5302,7 +5342,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5310,17 +5350,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -5536,7 +5581,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -5544,17 +5589,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -6091,7 +6141,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -6099,17 +6149,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6325,7 +6380,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6333,17 +6388,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -7907,7 +7967,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -7915,17 +7975,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8141,7 +8206,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -8149,17 +8214,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -8445,7 +8515,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -8453,17 +8523,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -8679,7 +8754,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -8687,17 +8762,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -9234,7 +9314,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -9242,17 +9322,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -9468,7 +9553,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -9476,17 +9561,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -11047,7 +11137,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -11055,17 +11145,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -11281,7 +11376,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -11289,17 +11384,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS62" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -11585,7 +11685,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -11593,17 +11693,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS64" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -11819,7 +11924,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -11827,17 +11932,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -12371,7 +12481,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -12379,17 +12489,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS68" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -12605,7 +12720,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -12613,17 +12728,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS69" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -14181,7 +14301,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
@@ -14189,17 +14309,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS79" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -14415,7 +14540,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
@@ -14423,17 +14548,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS80" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -14719,7 +14849,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
@@ -14727,17 +14857,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS82" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -14953,7 +15088,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
@@ -14961,17 +15096,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS83" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -15505,7 +15645,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
@@ -15513,17 +15653,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS86" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
       <c r="AT86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -15739,7 +15884,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
@@ -15747,17 +15892,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS87" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
       <c r="AT87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -17460,7 +17610,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
@@ -17468,17 +17618,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS98" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -17694,7 +17849,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
@@ -17702,17 +17857,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS99" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -17998,7 +18158,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ101" t="inlineStr">
@@ -18006,17 +18166,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS101" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -18232,7 +18397,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
@@ -18240,17 +18405,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS102" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -18784,7 +18954,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
@@ -18792,17 +18962,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS105" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -19018,7 +19193,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
@@ -19026,17 +19201,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS106" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -20047,7 +20227,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
@@ -20055,17 +20235,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS113" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -20281,7 +20466,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
@@ -20289,17 +20474,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS114" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -20585,7 +20775,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
@@ -20593,17 +20783,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS116" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -20819,7 +21014,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
@@ -20827,17 +21022,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS117" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -21371,7 +21571,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
@@ -21379,17 +21579,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS120" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -21605,7 +21810,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
@@ -21613,17 +21818,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS121" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -22634,7 +22844,7 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
@@ -22642,17 +22852,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS128" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
@@ -22868,7 +23083,7 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
@@ -22876,17 +23091,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS129" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -23027,7 +23247,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
@@ -23035,17 +23255,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS130" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -23261,7 +23486,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
@@ -23269,17 +23494,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS131" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
